--- a/Training Data/Automation/LRL.xlsx
+++ b/Training Data/Automation/LRL.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\SMS_Automation\Training Data\Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A81F15BD-9206-46F2-8CB0-A2C616EA408C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18039C31-3F48-4228-A30F-E30D5FB3AF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LRL" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="83">
-  <si>
-    <t>SL No</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
   <si>
     <t>Request</t>
   </si>
@@ -31,228 +28,87 @@
     <t>Reply</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>LRL 01947237994</t>
-  </si>
-  <si>
-    <t>MSISDN: 8801947237994, Datetime: 20260607213918, LAC ID: 678, Cell ID: 64853, Address: East Rupatoli, 24 no. Ward, P.S: Kotowali, Barisal Sadar, Barisal, BPARTY: 88042616E676C616, IMEI: 860067073634400, IMSI: 470039948287002, UsageType: SMSMT, NetworkType: 2G. - Banglalink | MN: 8801947237994, LAC/eNodeB_ID: 678, Cell Name: BAR_W0486_3 (Cell ID: 64853), Status: Attached, LRA: 2026-06-07 21:50:51+06:00, Add: East Rupatoli 24 no. Ward P.S: Kotowali Barisal Sadar Barisal, Lat: 22.661409, Long: 90.349411 - Banglalink</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>LRL 01617610134</t>
-  </si>
-  <si>
-    <t>MSISDN: 8801617610134, MSISDN B Party: 8801723599495, Last Call location: Ward No 24, BARISAL SADAR KOTWALI, Barisal, LAC ID: 8005, Cell ID: 28196, Lat_Long: 22.66143, 90.3495, Date_time: 20260607205630, IMEI: 860068048764800, IMSI: 470075012337288 [Robi] | RADIO LOCATION: Ward No-24, Barisal Sadar (kotwali), Barisal, LAC ID: 8005, CELL ID: 28196, LAT, LONG: 22.66143, 90.3495, MS STATUS: Attached, LAST ACTION TIME: 2026-06-07 21:37:12 [Robi]</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>LRL 01316178945</t>
-  </si>
-  <si>
-    <t>8801316178945 / 8801323428959, MTC, 07/06/2026 19:49:15, [23093 53640], PASCHIM CHAR DAPDAPIA, DAPDAPIA, NALCHITY, JHALOKATI, IMEI: 868236085902400, IMSI: 470010491153713 [GP] | MSISDN: 8801316178945, LastActiveDateTime: 2026-06-07 22:30:50, LACID: 48261, CellID: 35855137, Latitude: 22.658194, Longitude: 90.344889, Address: 13, PARARA ROAD, P.S. KOTOWALI, DIST. BARISAL, CS Status: Idle [GP]</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>LRL 01779398037</t>
-  </si>
-  <si>
-    <t>8801779398037, 4750, SMSMT, 07/06/2026 23:25:34, [56312 25735199], HOLDING NO. 54/1, FAKIRAPUL, DHAKA, IMEI: 359127131839920, IMSI: 470010441603444 [GP] | MSISDN: 8801779398037, LastActiveDateTime: 2026-06-07 23:35:36, LACID: 56312, CellID: 25850635, Latitude: 23.735361, Longitude: 90.416222, Address: 38, NAYAPALTAN, DHAKA-1000, CS Status: Idle [GP]</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>LRL 01724034442</t>
   </si>
   <si>
     <t>No RL Info Found of 1724034442 [GP]</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>LRL 01868577041</t>
   </si>
   <si>
     <t>MSISDN: 8801868577041, RADIO LOCATION: Kashipur, Barisal Sadar (kotwali), Barisal, Barisal, LAC ID: 8006, CELL ID: 28105, LAT, LONG: 22.73461111, 90.33791667, MS STATUS: Attached, LAST ACTION TIME: 2026-06-08 07:50:46 [Robi]</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>LRL 01322350825</t>
   </si>
   <si>
     <t>MSISDN: 8801322350825, LastActiveDateTime: 2026-06-08 13:34:43, LACID: 56382, CellID: 25739297, Latitude: 23.725278, Longitude: 90.411111, Address: 5, BANGABANDHU AVENUE, DHAKA-100, CS Status: Idle, Volte Status: not in VoLTE network [GP]</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>LRL 01919904263</t>
-  </si>
-  <si>
-    <t>MN: 01919904263 No Radio Location Found. - Banglalink | MSISDN: 8801919904263, Datetime: 20260605152339, LAC ID: 680, Cell ID: 46521, Address: Vill: Hayatsar, PO: Churamon, PS: Kawnia, Dist: Barisal, BPARTY: 8804D79424C20417, IMEI: 864434060146480, IMSI: 470039934828149, UsageType: SMSMT, NetworkType: 2G. - Banglalink</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>LRL 01612196151</t>
   </si>
   <si>
     <t>MSISDN: 8801612196151, RADIO LOCATION: (no specific location), MS STATUS: Attached, LAST ACTION TIME: 2026-06-08 15:15:55 [Robi]</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>LRL 01816906726</t>
   </si>
   <si>
     <t>MSISDN: 8801816906726, RADIO LOCATION: Number is out of network. LAST ATTACHED DATE &amp; TIME: 2026-06-08 15:30:01 [Robi]</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>LRL 01785251167</t>
-  </si>
-  <si>
-    <t>8801785251167, GP Info, SMSMT, 09/06/2026 13:01:08, [46051 28701471], RAJAPUR BAZAR, RAJAPUR BAZAR, RAJAPUR, JHALOKATHI, IMEI: 353000330191940, IMSI: 470010457776282 [GP] | MSISDN: 8801785251167, LastActiveDateTime: 2026-06-08 18:26:20, LACID: 46051, CellID: 28701471, Latitude: 22.570722, Longitude: 90.139278, Address: RAJAPUR BAZAR, RAJAPUR BAZAR, RAJAPUR, JHALOKATHI, CS Status: Idle [GP]</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>LRL 01941295521</t>
-  </si>
-  <si>
-    <t>MSISDN: 8801941295521, Datetime: 20260608172039, LAC ID: 680, Cell ID: 63091, Address: Ayar bazar, Syedkathi, Banaripara, Barisal, BPARTY: 8801979415850, IMEI: 861675072375840, IMSI: 470039907908432, UsageType: SMSMT, NetworkType: 2G. - Banglalink</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>LRL 01302981818</t>
   </si>
   <si>
     <t>MSISDN: 8801302981818, LastActiveDateTime: 2026-06-08 18:47:30, LACID: 23102, CellID: 41905, Latitude: 22.752528, Longitude: 89.686667, Address: LAL CHONDROPUR, GABKHALI, FAKIRHAT, BAGERHAT, CS Status: Idle, Volte Status: N/A [GP]</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>LRL 01838880159</t>
   </si>
   <si>
     <t>MSISDN: 8801838880159, RADIO LOCATION: Number is out of network. LAST ATTACHED DATE &amp; TIME: 2026-06-09 19:08:58 [Robi]</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>LRL 01872664308</t>
   </si>
   <si>
     <t>MSISDN: 8801872664308, RADIO LOCATION: Number is out of network. LAST ATTACHED DATE &amp; TIME: 2026-06-08 22:38:51 [Robi]</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
     <t>LRL 01648051331</t>
   </si>
   <si>
     <t>MSISDN: 8801648051331, RADIO LOCATION: Ward No-40 (Part), Mohammadpur, Dhaka, Dhaka, LAC ID: 108, CELL ID: 21724, LAT, LONG: 23.754868, 90.381101, MS STATUS: Attached, LAST ACTION TIME: 2026-06-09 22:00:58 [Robi]</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
     <t>LRL 01642348522</t>
   </si>
   <si>
     <t>MSISDN: 8801642348522, RADIO LOCATION: Sarikal, Gaurnadi, Barisal, Barisal, LAC ID: 8004, CELL ID: 28037, LAT, LONG: 22.89985817, 90.30252928, MS STATUS: Attached, LAST ACTION TIME: 2026-06-09 22:59:24 [Robi]</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>MSISDN: 8801642348522, RADIO LOCATION: Sarikal, Gaurnadi, Barisal, Barisal, LAC ID: 8004, CELL ID: 28037, LAT, LONG: 22.89985817, 90.30252928, MS STATUS: Attached, LAST ACTION TIME: 2026-06-09 19:36:32 [Robi]</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>LRL 01739204760</t>
-  </si>
-  <si>
-    <t>MSISDN: 8801739204760, LastActiveDateTime: 2026-06-09 21:35:03, LACID: 48251, CellID: 29773089, Latitude: 22.7178, Longitude: 90.3671, Address: SHER-E-BANGLA ROAD, KASHIPUR, CHOHUTPUR, BARISAL SADAR, BARISAL, CS Status: Idle, Volte Status: not in VoLTE network [GP] | 8801739204760, GP Info, SMSMT, 09/06/2026 19:30:37, [48251 29773129], SHER-E-BANGLA ROAD, KASHIPUR, CHOHUTPUR, BARISAL SADAR, BARISAL, IMEI: 868126062531170, IMSI: 470010394505884 [GP]</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>LRL 01815251167</t>
-  </si>
-  <si>
-    <t>(Reply included with LRL 01785251167 batch)</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
     <t>LRL 01631371920</t>
   </si>
   <si>
     <t>MSISDN: 8801631371920, RADIO LOCATION: Number is not in use. [Robi]</t>
   </si>
   <si>
-    <t>24</t>
-  </si>
-  <si>
     <t>LRL 01881971315</t>
   </si>
   <si>
     <t>MSISDN: 8801881971315, RADIO LOCATION: Number is not in use. [Robi]</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>LRL 01319472535</t>
-  </si>
-  <si>
-    <t>8801319472535 / 8801737374588, MOC, 08/06/2026 23:24:03, [23123 20926], VILL SOUTH DHUASHAR, P.O. DHUASAR, UNION 5 BALIGRAM, P.S. KALKINI, MADARIPUR, IMEI: 357726270741110, IMSI: 470010402936218 [GP]</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
     <t>LRL 01937344944</t>
   </si>
   <si>
     <t>MN: 01937344944 No Radio Location Found. - Banglalink</t>
   </si>
   <si>
-    <t>27</t>
-  </si>
-  <si>
     <t>LRL 01327655002</t>
   </si>
   <si>
@@ -262,13 +118,98 @@
     <t>LRL 01403710124</t>
   </si>
   <si>
-    <t>MN: 8801403710124, LAC/eNodeB_ID: 11619, Cell Name: DHK_L1619_221 (Cell ID: 221), Status: Attached, LRA: 2026-06-10 22:07:04+06:00, Add: Md. Anwar Karim Bhuiya Vill-Bhali P.O-Bhulta P.S-Rupganj Narayanganj, Lat: 23.78632, Long: 90.55426 - Banglalink | MSISDN: 8801403710124 Task failed to execute. No data returned. - Banglalink</t>
-  </si>
-  <si>
-    <t>LRL 01865686408</t>
-  </si>
-  <si>
-    <t>(New request - reply not yet visible)</t>
+    <t>MN: 8801965308627, LAC/eNodeB_ID: 10209, Cell Name: DHK_L0523 (Cell ID: 135), Status: Attached, LRA: 2026-06-19 17:23:01+06:00, Add: Abdul Jalil Talukdar, Durgapur Bajar, Durgapur, Netrokona,Durgapur_Netrakona,Netrakona, Lat: 25.1246, Long: 90.6777 - Banglalink</t>
+  </si>
+  <si>
+    <t>LRL 01965308627</t>
+  </si>
+  <si>
+    <t>LRL 01931388798</t>
+  </si>
+  <si>
+    <t>MN: 8801931388798, LAC/eNodeB_ID: 173, Cell Name: DHK_X0743_3 (Cell ID: 17423), Status: Attached, LRA: 2026-06-15 00:25:45+06:00, Add: NandoKanon1300North South Road Polaspur East Donia Shyampur Dhaka,Kadamtali,Dhaka, Lat: 23.69967, Long: 90.45347 - Banglalink</t>
+  </si>
+  <si>
+    <t>LRL 01921797846</t>
+  </si>
+  <si>
+    <t>MN: 01921797846 No Radio Location Found. - Banglalink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MN: 8801403710124, LAC/eNodeB_ID: 11619, Cell Name: DHK_L1619_221 (Cell ID: 221), Status: Attached, LRA: 2026-06-10 22:07:04+06:00, Add: Md. Anwar Karim Bhuiya Vill-Bhali P.O-Bhulta P.S-Rupganj Narayanganj, Lat: 23.78632, Long: 90.55426 - Banglalink </t>
+  </si>
+  <si>
+    <t>LRL 01711568316</t>
+  </si>
+  <si>
+    <t>MSISDN: 8801711568316
+LastActiveDateTime: 2026-06-15 15:47:18 06:00
+LACID: 48251
+CellID: 35852577
+Latitude: 22.700083
+Longitude: 90.3645
+Address: NORTH ALEKANDA; NEW ASHRAF RD,BARISAL SADAR,BARISAL,BARISAL
+CS Status: Idle
+Volte Status: not in VoLTE network [GP]</t>
+  </si>
+  <si>
+    <t>LRL 01744708168</t>
+  </si>
+  <si>
+    <t>MSISDN: 8801744708168
+LastActiveDateTime: 2026-06-15 04:33:18 06:00
+LACID: 21025
+CellID: 34032
+Latitude: 23.77964
+Longitude: 90.24752
+Address: JHAUCHAR BAZAR, HEMAYETPUR BAZAR, SAVAR,
+CS Status: Idle
+Volte Status: N/A [GP]</t>
+  </si>
+  <si>
+    <t>LRL 01335578187</t>
+  </si>
+  <si>
+    <t>MSISDN: 8801335578187
+LastActiveDateTime: 2026-06-16 00:06:43 06:00
+LACID: 46481
+CellID: 29557517
+Latitude: 23.08075
+Longitude: 90.422333
+Address: VILL: DHIPUR PO: GOSAIRHAT  PS: GOSAIRHAT  DIST:SHARIATPUR
+CS Status: Idle
+Volte Status: not in VoLTE network [GP]</t>
+  </si>
+  <si>
+    <t>LRL 01343850025</t>
+  </si>
+  <si>
+    <t>MSISDN: 8801343850025
+LastActiveDateTime: 2026-06-16 09:20:20 06:00
+LACID: 46331
+CellID: 29666059
+Latitude: 22.807177
+Longitude: 90.332201
+Address: KALIKAPUR,BABUGANJ,BARISAL
+CS Status: Idle
+Volte Status: not in VoLTE network [GP]</t>
+  </si>
+  <si>
+    <t>MSISDN: 8801340484381
+LastActiveDateTime: 2026-06-16 15:53:27 06:00
+LACID: 48251
+CellID: 35851789
+Latitude: 22.715444
+Longitude: 90.348778
+Address: SARNA MANSION; NATULLAHBAD BUS STAND; KASHIPUR,BARISAL SADAR,BARISAL SADAR,BARISAL
+CS Status: Idle
+Volte Status: not in VoLTE network [GP]</t>
+  </si>
+  <si>
+    <t>LRL 01340484381</t>
+  </si>
+  <si>
+    <t>SL NO</t>
   </si>
 </sst>
 </file>
@@ -417,7 +358,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -597,8 +538,20 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -713,6 +666,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -758,7 +724,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -766,8 +732,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -814,15 +789,12 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="2">
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -838,10 +810,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{88E374DA-405A-4DC8-B21C-4FF654D8A2E5}" name="Table1" displayName="Table1" ref="A1:C28" totalsRowShown="0">
-  <autoFilter ref="A1:C28" xr:uid="{88E374DA-405A-4DC8-B21C-4FF654D8A2E5}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{996EE604-DB90-478D-8FA9-4A7A37E1F843}" name="SL No" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{88E374DA-405A-4DC8-B21C-4FF654D8A2E5}" name="Table1" displayName="Table1" ref="B1:C25" totalsRowShown="0">
+  <autoFilter ref="B1:C25" xr:uid="{88E374DA-405A-4DC8-B21C-4FF654D8A2E5}"/>
+  <tableColumns count="2">
     <tableColumn id="2" xr3:uid="{E0F362AA-4610-478F-8159-66CC4C6C880B}" name="Request" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{94CD0292-BA4E-4F77-96F0-3A8528585552}" name="Reply" dataDxfId="0"/>
   </tableColumns>
@@ -1166,320 +1137,287 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="8.83984375" style="3"/>
-    <col min="2" max="2" width="20.3125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="58.05078125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" style="5"/>
+    <col min="2" max="2" width="20.31640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="58.04296875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="129.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:3" ht="59" x14ac:dyDescent="0.75">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="100.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="3" t="s">
+    <row r="4" spans="1:3" ht="59" x14ac:dyDescent="0.75">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="100.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="6" spans="1:3" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="86.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="3" t="s">
+    <row r="7" spans="1:3" ht="59" x14ac:dyDescent="0.75">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="1" t="s">
+    </row>
+    <row r="8" spans="1:3" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="3" t="s">
+      <c r="C8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="57.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="3" t="s">
+    <row r="10" spans="1:3" ht="59" x14ac:dyDescent="0.75">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="59" x14ac:dyDescent="0.75">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="57.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="3" t="s">
+    <row r="12" spans="1:3" ht="59" x14ac:dyDescent="0.75">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="59" x14ac:dyDescent="0.75">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="59" x14ac:dyDescent="0.75">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="73.75" x14ac:dyDescent="0.75">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="73.75" x14ac:dyDescent="0.75">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="147.5" x14ac:dyDescent="0.75">
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="132.75" x14ac:dyDescent="0.75">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="147.5" x14ac:dyDescent="0.75">
+      <c r="A23" s="4">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="132.75" x14ac:dyDescent="0.75">
+      <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="B24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="147.5" x14ac:dyDescent="0.75">
+      <c r="A25" s="4">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="100.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="57.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="57.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="B25" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="57.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="57.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="3" t="s">
+      <c r="C25" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="57.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="115.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="57.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="57.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="86.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
   </sheetData>
